--- a/TuningResults.xlsx
+++ b/TuningResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BB0742-A23B-411A-8353-B57643F57FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462707E7-898E-4A10-96E9-05656F059BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09F9910B-DC95-4A40-9207-E388BF1B80D2}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28320" xr2:uid="{09F9910B-DC95-4A40-9207-E388BF1B80D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t> Stomach</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Modified Reference Man Values</t>
+  </si>
+  <si>
+    <t>range of MRMV</t>
+  </si>
+  <si>
+    <t>Tuning STD</t>
   </si>
 </sst>
 </file>
@@ -163,7 +169,17 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.8616688707440078E-2"/>
+          <c:y val="3.1040567822418621E-2"/>
+          <c:w val="0.88467555577124513"/>
+          <c:h val="0.79091277933733606"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -246,43 +262,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.20899999999999999</c:v>
+                  <c:v>0.86</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.968</c:v>
+                  <c:v>2.56</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.1680000000000001</c:v>
+                  <c:v>3.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.69699999999999995</c:v>
+                  <c:v>2.04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.9929999999999899</c:v>
+                  <c:v>10.09</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.89700000000000002</c:v>
+                  <c:v>2.08</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.7190000000000003</c:v>
+                  <c:v>11.79</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13.215999999999999</c:v>
+                  <c:v>9.4499999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.34499999999999997</c:v>
+                  <c:v>0.78</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.75800000000000001</c:v>
+                  <c:v>1.85</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.0979999999999999</c:v>
+                  <c:v>9.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38.191000000000003</c:v>
+                  <c:v>8.98</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>30.741</c:v>
+                  <c:v>36.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -298,7 +314,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
+              <c:f>Sheet1!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -317,6 +333,120 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:f>Sheet1!$F$2:$F$14</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="13"/>
+                  <c:pt idx="0">
+                    <c:v>0.15999999999999992</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.27</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0.4700000000000002</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0.22999999999999998</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>4.1999999999999993</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.83000000000000007</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>1.6600000000000001</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>2.1500000000000004</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>7.999999999999996E-2</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>0.44999999999999996</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>2.8</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>6.3900000000000006</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>10.909999999999997</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:f>Sheet1!$E$2:$E$14</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="13"/>
+                  <c:pt idx="0">
+                    <c:v>0.43999999999999995</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.83000000000000007</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3.0300000000000002</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>1.77</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>2.8000000000000007</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.7699999999999998</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>6.34</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>2.8499999999999996</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>0.52</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>0.25</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>3.2</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>7.6099999999999994</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>15.090000000000003</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$2:$A$14</c:f>
@@ -366,7 +496,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$14</c:f>
+              <c:f>Sheet1!$D$2:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1223,15 +1353,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>566737</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>638174</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>819149</xdr:colOff>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1577,10 +1707,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B989AF-11C6-4973-98C8-CD4239AA27BC}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1588,150 +1724,305 @@
         <v>13</v>
       </c>
       <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
         <v>15</v>
       </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.20899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="C2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D2">
         <v>1.24</v>
       </c>
+      <c r="E2">
+        <f>$D$2-0.8</f>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="F2">
+        <f>ABS(D2-1.4)</f>
+        <v>0.15999999999999992</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3">
-        <v>1.968</v>
+        <v>2.56</v>
       </c>
       <c r="C3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D3">
         <v>1.03</v>
       </c>
+      <c r="E3">
+        <f>D3-0.2</f>
+        <v>0.83000000000000007</v>
+      </c>
+      <c r="F3">
+        <f>ABS(D3-1.3)</f>
+        <v>0.27</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B4">
-        <v>2.1680000000000001</v>
+        <v>3.52</v>
       </c>
       <c r="C4">
+        <v>0.99</v>
+      </c>
+      <c r="D4">
         <v>3.93</v>
       </c>
+      <c r="E4">
+        <f>D4-0.9</f>
+        <v>3.0300000000000002</v>
+      </c>
+      <c r="F4">
+        <f>4.4-D4</f>
+        <v>0.4700000000000002</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>0.69699999999999995</v>
+        <v>2.04</v>
       </c>
       <c r="C5">
+        <v>0.41</v>
+      </c>
+      <c r="D5">
         <v>2.27</v>
       </c>
+      <c r="E5">
+        <f>D5-0.5</f>
+        <v>1.77</v>
+      </c>
+      <c r="F5">
+        <f>2.5-D5</f>
+        <v>0.22999999999999998</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B6">
-        <v>1.9929999999999899</v>
+        <v>10.09</v>
       </c>
       <c r="C6">
+        <v>2.14</v>
+      </c>
+      <c r="D6">
         <v>9.3000000000000007</v>
       </c>
+      <c r="E6">
+        <f>D6-6.5</f>
+        <v>2.8000000000000007</v>
+      </c>
+      <c r="F6">
+        <f>13.5-D6</f>
+        <v>4.1999999999999993</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B7">
-        <v>0.89700000000000002</v>
+        <v>2.08</v>
       </c>
       <c r="C7">
+        <v>0.63</v>
+      </c>
+      <c r="D7">
         <v>2.0699999999999998</v>
       </c>
+      <c r="E7">
+        <f>D7-1.3</f>
+        <v>0.7699999999999998</v>
+      </c>
+      <c r="F7">
+        <f>2.9-D7</f>
+        <v>0.83000000000000007</v>
+      </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B8">
-        <v>4.7190000000000003</v>
+        <v>11.79</v>
       </c>
       <c r="C8">
+        <v>2.09</v>
+      </c>
+      <c r="D8">
         <v>10.34</v>
       </c>
+      <c r="E8">
+        <f>D8-4</f>
+        <v>6.34</v>
+      </c>
+      <c r="F8">
+        <f>12-D8</f>
+        <v>1.6600000000000001</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B9">
-        <v>13.215999999999999</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="C9">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="D9">
         <v>10.85</v>
       </c>
+      <c r="E9">
+        <f>D9-8</f>
+        <v>2.8499999999999996</v>
+      </c>
+      <c r="F9">
+        <f>13-D9</f>
+        <v>2.1500000000000004</v>
+      </c>
     </row>
-    <row r="10" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10">
-        <v>0.34499999999999997</v>
+        <v>0.78</v>
       </c>
       <c r="C10">
+        <v>0.19</v>
+      </c>
+      <c r="D10">
         <v>0.62</v>
       </c>
+      <c r="E10">
+        <f>D10-0.1</f>
+        <v>0.52</v>
+      </c>
+      <c r="F10">
+        <f>0.7-D10</f>
+        <v>7.999999999999996E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11">
-        <v>0.75800000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="C11">
+        <v>0.5</v>
+      </c>
+      <c r="D11">
         <v>1.45</v>
       </c>
+      <c r="E11">
+        <f>D11-1.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="F11">
+        <f>1.9-D11</f>
+        <v>0.44999999999999996</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12">
-        <v>4.0979999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="C12">
+        <v>2.11</v>
+      </c>
+      <c r="D12">
         <v>6.2</v>
       </c>
+      <c r="E12">
+        <f>D12-3</f>
+        <v>3.2</v>
+      </c>
+      <c r="F12">
+        <f>9-D12</f>
+        <v>2.8</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13">
-        <v>38.191000000000003</v>
+        <v>8.98</v>
       </c>
       <c r="C13">
+        <v>2.16</v>
+      </c>
+      <c r="D13">
         <v>18.61</v>
       </c>
+      <c r="E13">
+        <f>D13-11</f>
+        <v>7.6099999999999994</v>
+      </c>
+      <c r="F13">
+        <f>25-D13</f>
+        <v>6.3900000000000006</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14">
-        <v>30.741</v>
+        <v>36.58</v>
       </c>
       <c r="C14">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="D14">
         <v>32.090000000000003</v>
+      </c>
+      <c r="E14">
+        <f>D14-17</f>
+        <v>15.090000000000003</v>
+      </c>
+      <c r="F14">
+        <f>43-D14</f>
+        <v>10.909999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f>SUM(B2:B14)</f>
+        <v>99.98</v>
       </c>
     </row>
   </sheetData>

--- a/TuningResults.xlsx
+++ b/TuningResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462707E7-898E-4A10-96E9-05656F059BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B3F3C0-20CD-4766-AFBC-544C11E0627C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28320" xr2:uid="{09F9910B-DC95-4A40-9207-E388BF1B80D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09F9910B-DC95-4A40-9207-E388BF1B80D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,10 +200,14 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -325,10 +329,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="bg1"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -435,7 +441,7 @@
             </c:minus>
             <c:spPr>
               <a:noFill/>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -725,19 +731,82 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10580401625686843"/>
+          <c:y val="5.1283692976279903E-2"/>
+          <c:w val="0.48459454399082375"/>
+          <c:h val="4.7201334764707156E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1356,13 +1425,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>638174</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>819149</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/TuningResults.xlsx
+++ b/TuningResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B3F3C0-20CD-4766-AFBC-544C11E0627C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462707E7-898E-4A10-96E9-05656F059BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09F9910B-DC95-4A40-9207-E388BF1B80D2}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28320" xr2:uid="{09F9910B-DC95-4A40-9207-E388BF1B80D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,14 +200,10 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -329,12 +325,10 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -441,7 +435,7 @@
             </c:minus>
             <c:spPr>
               <a:noFill/>
-              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -731,82 +725,19 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="3175">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
+        <a:ln>
+          <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:legendEntry>
-        <c:idx val="0"/>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="1"/>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-      </c:legendEntry>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.10580401625686843"/>
-          <c:y val="5.1283692976279903E-2"/>
-          <c:w val="0.48459454399082375"/>
-          <c:h val="4.7201334764707156E-2"/>
-        </c:manualLayout>
-      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1425,13 +1356,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>638174</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>819149</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
